--- a/Data/03_Ground_Truth_Datensatz.xlsx
+++ b/Data/03_Ground_Truth_Datensatz.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,35 +451,50 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>PLZ4</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>ORT</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>lat_api</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>lon_api</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>BAUJAHR_API</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>BAUJAHR_KATEGORIE</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>HAUPTNUTZUNG</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>NUTZUNG_KATEGORIE</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>GS_EIGENTUMSKATEGORIE</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Fenster_KATEGORIE</t>
         </is>
@@ -502,35 +517,44 @@
       <c r="D2" t="n">
         <v>14</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>8409</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>Winterthur</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
+        <v>47.50180435180664</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8.773800849914551</v>
+      </c>
+      <c r="I2" t="n">
         <v>1993</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>1981-2000</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Industrie und Gerwerbe</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Gewerbehaus</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Immobilien</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Ab 1990</t>
         </is>
@@ -553,35 +577,44 @@
       <c r="D3" t="n">
         <v>66</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="n">
+        <v>8408</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Winterthur</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
+        <v>47.50725936889648</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8.693532943725586</v>
+      </c>
+      <c r="I3" t="n">
         <v>2017</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>2001-2024</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Industrie und Gerwerbe</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Sonstige</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Übrige</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Ab 1990</t>
         </is>
@@ -604,35 +637,44 @@
       <c r="D4" t="n">
         <v>69</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="n">
+        <v>8400</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Winterthur</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
+        <v>47.50235748291016</v>
+      </c>
+      <c r="H4" t="n">
+        <v>8.731490135192871</v>
+      </c>
+      <c r="I4" t="n">
         <v>1869</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>1851-1900</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Verwaltungsgebäude und Gebäude mit öffentlichem Charakter</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Turnhalle</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Schulamt</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Bevor 1990</t>
         </is>
@@ -655,35 +697,44 @@
       <c r="D5" t="n">
         <v>54</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="n">
+        <v>8404</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Winterthur</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
+        <v>47.51273727416992</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8.758280754089355</v>
+      </c>
+      <c r="I5" t="n">
         <v>1945</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>1901-1945</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Verwaltungsgebäude und Gebäude mit öffentlichem Charakter</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Kindergarten</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Schulamt</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Bevor 1990</t>
         </is>
@@ -706,35 +757,44 @@
       <c r="D6" t="n">
         <v>3</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="n">
+        <v>8400</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Winterthur</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
+        <v>47.49460601806641</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8.736106872558594</v>
+      </c>
+      <c r="I6" t="n">
         <v>1960</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>1946-1960</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Verwaltungsgebäude und Gebäude mit öffentlichem Charakter</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Schulhaus</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Schulamt</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Bevor 1990</t>
         </is>
@@ -757,35 +817,44 @@
       <c r="D7" t="n">
         <v>54</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="n">
+        <v>8400</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Winterthur</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
+        <v>47.4957160949707</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8.736516952514648</v>
+      </c>
+      <c r="I7" t="n">
         <v>1962</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>1961-1980</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Verwaltungsgebäude und Gebäude mit öffentlichem Charakter</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Sonstige</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Immobilien</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Bevor 1990</t>
         </is>
@@ -808,35 +877,44 @@
       <c r="D8" t="n">
         <v>4</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" t="n">
+        <v>8400</v>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>Winterthur</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
+        <v>47.49843597412109</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8.72664737701416</v>
+      </c>
+      <c r="I8" t="n">
         <v>1965</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>1961-1980</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Verwaltungsgebäude und Gebäude mit öffentlichem Charakter</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Sonstige</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Immobilien</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Bevor 1990</t>
         </is>
@@ -859,35 +937,44 @@
       <c r="D9" t="n">
         <v>7</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" t="n">
+        <v>8400</v>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>Winterthur</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
+        <v>47.49327087402344</v>
+      </c>
+      <c r="H9" t="n">
+        <v>8.733986854553223</v>
+      </c>
+      <c r="I9" t="n">
         <v>1993</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>1981-2000</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Verwaltungsgebäude und Gebäude mit öffentlichem Charakter</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Sonstige</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Immobilien</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Ab 1990</t>
         </is>
@@ -910,35 +997,44 @@
       <c r="D10" t="n">
         <v>32</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" t="n">
+        <v>8405</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>Winterthur</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
+        <v>47.48353958129883</v>
+      </c>
+      <c r="H10" t="n">
+        <v>8.764111518859863</v>
+      </c>
+      <c r="I10" t="n">
         <v>2018</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>2001-2024</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Verwaltungsgebäude und Gebäude mit öffentlichem Charakter</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Schulhaus</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Schulamt</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Ab 1990</t>
         </is>
@@ -961,35 +1057,44 @@
       <c r="D11" t="n">
         <v>12</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" t="n">
+        <v>8400</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>Winterthur</t>
         </is>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
+        <v>47.49415969848633</v>
+      </c>
+      <c r="H11" t="n">
+        <v>8.732730865478516</v>
+      </c>
+      <c r="I11" t="n">
         <v>1863</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>1851-1900</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Wohngebäude</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Wohnhaus</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Immobilien</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Bevor 1990</t>
         </is>
@@ -1012,35 +1117,44 @@
       <c r="D12" t="n">
         <v>17</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" t="n">
+        <v>8400</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>Winterthur</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
+        <v>47.5031852722168</v>
+      </c>
+      <c r="H12" t="n">
+        <v>8.716382026672363</v>
+      </c>
+      <c r="I12" t="n">
         <v>1897</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>1851-1900</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Wohngebäude</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Wohnhaus</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Immobilien</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Bevor 1990</t>
         </is>
@@ -1063,35 +1177,44 @@
       <c r="D13" t="n">
         <v>45</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" t="n">
+        <v>8400</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>Winterthur</t>
         </is>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
+        <v>47.49171447753906</v>
+      </c>
+      <c r="H13" t="n">
+        <v>8.719482421875</v>
+      </c>
+      <c r="I13" t="n">
         <v>1908</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>1901-1945</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Wohngebäude</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Wohnhaus</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Immobilien</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Bevor 1990</t>
         </is>
@@ -1114,35 +1237,44 @@
       <c r="D14" t="n">
         <v>26</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" t="n">
+        <v>8404</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>Winterthur</t>
         </is>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
+        <v>47.51420211791992</v>
+      </c>
+      <c r="H14" t="n">
+        <v>8.761743545532227</v>
+      </c>
+      <c r="I14" t="n">
         <v>1964</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>1961-1980</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>Wohngebäude</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>Wohnhaus</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Immobilien</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Bevor 1990</t>
         </is>
@@ -1165,35 +1297,44 @@
       <c r="D15" t="n">
         <v>8</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" t="n">
+        <v>8405</v>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>Winterthur</t>
         </is>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
+        <v>47.48589324951172</v>
+      </c>
+      <c r="H15" t="n">
+        <v>8.770423889160156</v>
+      </c>
+      <c r="I15" t="n">
         <v>1983</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>1981-2000</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>Wohngebäude</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>Wohnhaus mit Schopf</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Immobilien</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Bevor 1990</t>
         </is>
@@ -1216,35 +1357,44 @@
       <c r="D16" t="n">
         <v>4</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" t="n">
+        <v>8408</v>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>Winterthur</t>
         </is>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
+        <v>47.51808929443359</v>
+      </c>
+      <c r="H16" t="n">
+        <v>8.692178726196289</v>
+      </c>
+      <c r="I16" t="n">
         <v>2024</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>2001-2024</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>Wohngebäude</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>Wohnhaus</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Immobilien</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Ab 1990</t>
         </is>
